--- a/data/employee_database.xlsx
+++ b/data/employee_database.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Employees" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,12 +471,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Years_Experience</t>
+          <t>Product_Team</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Performance_Rating</t>
+          <t>Certifications</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>Remote_Status</t>
         </is>
       </c>
     </row>
@@ -513,11 +513,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2019-03-15</t>
+          <t>2020-03-15</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>125000</v>
+        <v>145000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -526,25 +526,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Student Information System</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Peter Hall</t>
+          <t>Frank Miller</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Python, Java, AWS, Docker</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -561,21 +563,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Product Manager - SIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>95000</v>
+        <v>135000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -584,15 +586,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Student Information System</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>CSPO, PMP</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -602,7 +606,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SEO, Content Marketing, Analytics</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -624,16 +628,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Staff Engineer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2021-01-10</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110000</v>
+        <v>175000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -642,25 +646,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>AWS, GCP, Kubernetes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Peter Hall</t>
+          <t>Frank Miller</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Terraform</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -677,21 +683,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>District Success Manager</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>72000</v>
+        <v>85000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -700,15 +706,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7</v>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>K-12 Implementation Cert</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Salesforce, Negotiation</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -740,16 +748,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HR Specialist</t>
+          <t>HR Business Partner</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
+          <t>2019-04-05</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>68000</v>
+        <v>95000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -758,25 +766,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>SHRM-CP</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Quinn Young</t>
+          <t>Karen Martinez</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Recruiting, Onboarding</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -798,16 +808,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Junior Developer</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2017-08-22</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65000</v>
+        <v>195000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -816,25 +826,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Learning Management</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>AWS, Azure, CKAD</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -856,16 +868,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>FP&amp;A Analyst</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>85000</v>
+        <v>88000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -874,25 +886,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>CFA Level 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Rachel King</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Excel, Financial Modeling, SAP</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -909,21 +923,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Content Strategist</t>
+          <t>Senior Product Manager</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>78000</v>
+        <v>155000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -932,25 +946,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Enrollment</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>SAFe Agilist</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>Olivia Lewis</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Writing, Social Media, HubSpot</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -972,16 +988,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>130000</v>
+        <v>115000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -990,25 +1006,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Student Information System</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Peter Hall</t>
+          <t>Carol Williams</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Python, ML, TensorFlow, SQL</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1025,21 +1043,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Implementation Specialist</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>88000</v>
+        <v>78000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1048,25 +1066,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5</v>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>EdTech Certified</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Noah Clark</t>
+          <t>David Brown</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>B2B Sales, CRM</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1088,16 +1108,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>HR Director</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>62000</v>
+        <v>140000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1106,25 +1126,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>SHRM-SCP, PHR</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Quinn Young</t>
+          <t>CHRO</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Interviewing, ATS Systems</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1173,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1164,25 +1186,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>AWS, Python</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Peter Hall</t>
+          <t>Carol Williams</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Python, PostgreSQL, Redis</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1204,16 +1228,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Accountant</t>
+          <t>Revenue Analyst</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>75000</v>
+        <v>82000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1222,25 +1246,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>CPA</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Rachel King</t>
+          <t>Grace Wilson</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>QuickBooks, Payroll, Tax</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -1257,21 +1283,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2017-11-08</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>105000</v>
+        <v>125000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1280,25 +1306,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9</v>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>TOGAF, AWS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Rachel King</t>
+          <t>VP Solutions</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Team Leadership, Strategy</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1315,21 +1343,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SEO Specialist</t>
+          <t>Product Director</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
+          <t>2019-02-28</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>70000</v>
+        <v>165000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1338,25 +1366,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Pragmatic Marketing</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Google Ads, SEMrush</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1378,16 +1408,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>145000</v>
+        <v>130000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1396,25 +1426,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>12</v>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>CKA, AWS DevOps</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Rachel King</t>
+          <t>Carol Williams</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>System Design, Mentoring, Agile</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1431,21 +1463,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>92000</v>
+        <v>145000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1454,25 +1486,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>CISSP, CEH, CCSP</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Rachel King</t>
+          <t>CISO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Policy Development, Compliance</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1489,21 +1523,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>Compliance Manager</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2015-01-05</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>185000</v>
+        <v>110000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1512,25 +1546,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>15</v>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>CIPP/US, FERPA</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CLO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Strategic Planning, M&amp;A</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -1547,21 +1583,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>82000</v>
+        <v>105000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1570,25 +1606,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3</v>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Enrollment</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>React, Node.js</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Noah Clark</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Lead Generation, Networking</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1605,17 +1643,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Training Specialist</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1628,25 +1666,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>K-12 Trainer Cert</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>David Brown</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TypeScript, Vue, CSS</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
